--- a/presentations/heatmap_byhand/xlsx/baseline_methods/dread/mcp_sqlite_risk_rankings_dread.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/dread/mcp_sqlite_risk_rankings_dread.xlsx
@@ -1767,12 +1767,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1791,6 +1792,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1806,6 +1812,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D=10-4=6 A=9 R=9 E=9 Disc=9 → avg=8.4 → Critical (table enumeration, api_keys visible)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1821,6 +1832,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D=10-3=7 A=9 R=9 E=9 Disc=9 → avg=8.6 → Critical (schema recon on api_keys)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1836,6 +1852,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D=10+0=10 A=9 R=9 E=9 Disc=9 → avg=9.2 → Critical (api_keys read=catastrophic)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1851,6 +1872,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>D=min(10+1,10)=10 A=9(api_keys) R=9 E=9 Disc=9 → avg=9.2 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1866,6 +1892,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>D=10+0=10 A=9 R=9 E=9 Disc=9 → avg=9.2 → Critical (api_keys create_table path)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
@@ -1879,6 +1910,11 @@
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>D=min(10,5)=5 A=9 R=9 E=9 Disc=9 → avg=8.2 → Critical (capped by append_insight rule)</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1930,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1918,6 +1955,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1933,6 +1975,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D=9 A=8(conservative org-wide) R=9 E=9 Disc=9 → avg=8.8 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1948,6 +1995,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D=9 A=8 R=9 E=9 Disc=9 → avg=8.8 → Critical (salary, grant amounts, compliance)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1963,6 +2015,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D=10 A=8 R=9 E=9 Disc=9 → avg=9.0 → Critical (immediate full-system compromise)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1978,6 +2035,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>D=7 A=8 R=9 E=9 Disc=9 → avg=8.4 → Critical (IP, unpublished results)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -1993,6 +2055,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>D=3 A=8 R=9 E=9 Disc=9 → avg=7.6 → High (public output, limited incremental harm)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2008,6 +2075,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>D=5 A=8 R=9 E=9 Disc=9 → avg=8.0 → Critical (org structure reconnaissance)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2021,6 +2093,11 @@
       <c r="C8" s="10" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>D=4 A=8 R=9 E=9 Disc=9 → avg=7.8 → High (operational metadata, limited harm)</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2112,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2059,6 +2137,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -2074,6 +2157,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D=9 A=9 R=9 E=9 Disc=9 → avg=9.0 → Critical (PII + salary for all employees)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -2089,6 +2177,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D=6 A=7 R=9 E=9 Disc=9 → avg=8.0 → Critical (project metadata + timelines)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2104,6 +2197,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D=6 A=7 R=9 E=9 Disc=9 → avg=8.0 → Critical (mixed public/internal; research team)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -2119,6 +2217,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>D=6 A=6 R=9 E=9 Disc=9 → avg=7.8 → High (research results; IP exposure)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2134,6 +2237,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>D=3 A=5 R=9 E=9 Disc=9 → avg=7.0 → High (public academic output, minimal extra harm)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -2149,6 +2257,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>D=8 A=8 R=9 E=9 Disc=9 → avg=8.8 → Critical (financial data; fiduciary/compliance impact)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2162,6 +2275,11 @@
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>D=10 A=9 R=9 E=9 Disc=9 → avg=9.2 → Critical (credential exfiltration = maximum damage)</t>
         </is>
       </c>
     </row>
